--- a/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
+++ b/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
@@ -84,17 +84,19 @@
     <t>高</t>
   </si>
   <si>
-    <t xml:space="preserve">支持对于数组内嵌套对象field的select操作，如{ a:1, b:[{a:1,b:2},{a:2,b:3}]}的select操作{"b.a":null}，返回记录为：{b:[{a:1},{a:2}]}
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>7人天</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>已完成分析
 （mongodb也支持）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">支持对于数组内嵌套对象field的select操作，如
+{ a:1, b:[{a:1,b:2},{a:2,b:3}, {c:1}, 4 ]} 的select操作 {"b.a":null}，返回记录为：
+{b:[{a:1},{a:2},{}]}
+</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -604,12 +606,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="81">
+    <row r="2" spans="1:13" ht="94.5">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -625,13 +627,13 @@
         <v>16</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>12</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K2" s="6"/>
       <c r="L2" s="6"/>

--- a/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
+++ b/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
@@ -84,10 +84,6 @@
     <t>高</t>
   </si>
   <si>
-    <t>7人天</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>已完成分析
 （mongodb也支持）</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -97,6 +93,10 @@
 { a:1, b:[{a:1,b:2},{a:2,b:3}, {c:1}, 4 ]} 的select操作 {"b.a":null}，返回记录为：
 {b:[{a:1},{a:2},{}]}
 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4人天</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -225,7 +225,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -249,6 +249,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -611,7 +614,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -627,17 +630,19 @@
         <v>16</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>12</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K2" s="6"/>
       <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
+      <c r="M2" s="9">
+        <v>41985</v>
+      </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="2"/>

--- a/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
+++ b/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -97,6 +97,48 @@
   </si>
   <si>
     <t>4人天</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">需要对collection增加一种属性，只允许insert写操作，同时可以去掉OID索引
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>福建移动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陈子川</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中</t>
+  </si>
+  <si>
+    <t>正在分析</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">福建移动5台物理机（8核4线程，36磁盘，64G内存），一共36*5=180数据节点；业务为日志分析，导数日志400G花费1.5小时，数据节点CPU达到100%。业务采用主子表，每小时建1个子表，上层业务定期对子表进行计算，不存在update/delete操作；经测试，去除OID索引，性能可以提升一倍。
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>途牛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>王涛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">需要提供数据中心到数据中心备份的方案，两个数据中心带宽有限，要尽量节约带宽
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已分析三种方案，待与途牛确定交付时间和方案</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -225,7 +267,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -252,6 +294,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -644,30 +689,60 @@
         <v>41985</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
+    <row r="3" spans="1:13" ht="135">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="10">
+        <v>41983</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
       <c r="L3" s="7"/>
       <c r="M3" s="7"/>
     </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
+    <row r="4" spans="1:13" ht="54">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
+      <c r="D4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="10">
+        <v>41981</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>

--- a/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
+++ b/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -141,12 +141,20 @@
     <t>已分析三种方案，待与途牛确定交付时间和方案</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>SEQUOIADBMAINSTREAM-472</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.10SP2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -160,6 +168,14 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="4">
@@ -264,10 +280,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -299,8 +319,12 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -683,10 +707,14 @@
       <c r="J2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
+      <c r="K2" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>31</v>
+      </c>
       <c r="M2" s="9">
-        <v>41985</v>
+        <v>41986</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="135">
@@ -15564,8 +15592,11 @@
       <formula1>"高,中,低"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="K2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
+++ b/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
@@ -623,18 +623,19 @@
   <dimension ref="A1:M991"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="7.125" customWidth="1"/>
-    <col min="2" max="2" width="34.125" customWidth="1"/>
-    <col min="3" max="3" width="30.875" customWidth="1"/>
-    <col min="4" max="4" width="12.125" customWidth="1"/>
+    <col min="1" max="1" width="5.25" customWidth="1"/>
+    <col min="2" max="2" width="32.375" customWidth="1"/>
+    <col min="3" max="3" width="36" customWidth="1"/>
+    <col min="4" max="4" width="9.5" customWidth="1"/>
     <col min="5" max="5" width="8.875" customWidth="1"/>
-    <col min="6" max="6" width="13.125" customWidth="1"/>
+    <col min="6" max="6" width="11.25" customWidth="1"/>
+    <col min="7" max="7" width="6.5" customWidth="1"/>
     <col min="8" max="8" width="15.375" customWidth="1"/>
-    <col min="9" max="9" width="10.375" customWidth="1"/>
-    <col min="10" max="10" width="11.625" customWidth="1"/>
+    <col min="9" max="9" width="8.125" customWidth="1"/>
+    <col min="10" max="10" width="10.25" customWidth="1"/>
     <col min="11" max="11" width="15.875" customWidth="1"/>
-    <col min="12" max="12" width="13.375" customWidth="1"/>
-    <col min="13" max="13" width="14.875" customWidth="1"/>
+    <col min="12" max="12" width="11.5" customWidth="1"/>
+    <col min="13" max="13" width="12.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="26.25" customHeight="1" thickBot="1">

--- a/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
+++ b/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="47">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -147,6 +147,71 @@
   </si>
   <si>
     <t>1.10SP2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">python驱动的游标查询在遍历时如果遇到游标关闭会抛出异常，对开发者体验不够好，采用和sdb shell一致的方法实现
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>民生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陈子川</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提交jira单</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SEQUOIADBMAINSTREAM-500 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1人天</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">sdbimprt导入工具字段分隔符需要支持多字符，降低重复几率
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">在官网上下载的driver包中，应该带上samples文件夹，方面开发者使用
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SEQUOIADBMAINSTREAM-501 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">sdbimprt导入工具支持从管道导入数据（例如 sdbimprt --exec 'dbexprt xxxxx' 从执行的命令导入数据）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>低</t>
+  </si>
+  <si>
+    <t>用户在从db2等导入数据到sequoiadb时不需要让数据落地
+但需要考虑是否有其它的打印信息？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SEQUOIADBMAINSTREAM-502 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2人天</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">sdbexprt导入工具能增加过滤条件/排序条件
+</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -287,7 +352,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -320,6 +385,12 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -718,7 +789,7 @@
         <v>41986</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="135">
+    <row r="3" spans="1:13" ht="108">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -778,29 +849,65 @@
       <c r="L4" s="7"/>
       <c r="M4" s="7"/>
     </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
+    <row r="5" spans="1:13" ht="67.5">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
+      <c r="D5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="10">
+        <v>41982</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="K5" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="L5" s="7">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="M5" s="13">
+        <v>42050</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="40.5">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
+      <c r="D6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" s="10">
+        <v>41982</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="H6" s="2"/>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
@@ -808,29 +915,67 @@
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
     </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
+    <row r="7" spans="1:13" ht="40.5">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>39</v>
+      </c>
       <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
+      <c r="D7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="10">
+        <v>41982</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="L7" s="7">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="M7" s="13">
+        <v>42050</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="67.5">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="10">
+        <v>41982</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="H8" s="2"/>
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
@@ -838,20 +983,44 @@
       <c r="L8" s="7"/>
       <c r="M8" s="7"/>
     </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
+    <row r="9" spans="1:13" ht="40.5">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
+      <c r="D9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="10">
+        <v>41982</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="K9" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="L9" s="7">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="M9" s="13">
+        <v>42050</v>
+      </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="2"/>
@@ -15595,9 +15764,12 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="K2" r:id="rId1"/>
+    <hyperlink ref="K5" r:id="rId2"/>
+    <hyperlink ref="K7" r:id="rId3"/>
+    <hyperlink ref="K9" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
 </worksheet>
 </file>
 

--- a/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
+++ b/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="49">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -212,6 +212,13 @@
   <si>
     <t xml:space="preserve">sdbexprt导入工具能增加过滤条件/排序条件
 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拒绝</t>
+  </si>
+  <si>
+    <t>讨论结论是和mongodb保持一致，保持抛异常方式</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -15792,10 +15799,10 @@
         <v>23</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="J3" s="7" t="s">
         <v>37</v>

--- a/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
+++ b/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="2014年" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="51">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -219,6 +219,14 @@
   </si>
   <si>
     <t>讨论结论是和mongodb保持一致，保持抛异常方式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1人天</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SEQUOIADBMAINSTREAM-578 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -698,7 +706,7 @@
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="A1:M991"/>
+  <dimension ref="A1:M990"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.25" customWidth="1"/>
@@ -757,74 +765,74 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="108">
+    <row r="2" spans="1:13" ht="54">
       <c r="A2" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>25</v>
-      </c>
+      <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F2" s="10">
-        <v>41983</v>
+        <v>41981</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
-      <c r="I2" s="7"/>
+      <c r="I2" s="7" t="s">
+        <v>12</v>
+      </c>
       <c r="J2" s="7"/>
       <c r="K2" s="7"/>
       <c r="L2" s="7"/>
       <c r="M2" s="7"/>
     </row>
-    <row r="3" spans="1:13" ht="54">
+    <row r="3" spans="1:13" ht="40.5">
       <c r="A3" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F3" s="10">
-        <v>41981</v>
+        <v>41982</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="H3" s="2"/>
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
       <c r="L3" s="7"/>
       <c r="M3" s="7"/>
     </row>
-    <row r="4" spans="1:13" ht="40.5">
+    <row r="4" spans="1:13" ht="67.5">
       <c r="A4" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
-      <c r="C4" s="2"/>
+      <c r="C4" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="D4" s="2" t="s">
         <v>33</v>
       </c>
@@ -835,7 +843,7 @@
         <v>41982</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="7"/>
@@ -844,28 +852,14 @@
       <c r="L4" s="7"/>
       <c r="M4" s="7"/>
     </row>
-    <row r="5" spans="1:13" ht="67.5">
-      <c r="A5" s="2">
-        <v>7</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" s="10">
-        <v>41982</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>42</v>
-      </c>
+    <row r="5" spans="1:13">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="7"/>
       <c r="J5" s="7"/>
@@ -15648,28 +15642,13 @@
       <c r="L990" s="7"/>
       <c r="M990" s="7"/>
     </row>
-    <row r="991" spans="1:13">
-      <c r="A991" s="2"/>
-      <c r="B991" s="2"/>
-      <c r="C991" s="2"/>
-      <c r="D991" s="2"/>
-      <c r="E991" s="2"/>
-      <c r="F991" s="2"/>
-      <c r="G991" s="2"/>
-      <c r="H991" s="2"/>
-      <c r="I991" s="7"/>
-      <c r="J991" s="7"/>
-      <c r="K991" s="7"/>
-      <c r="L991" s="7"/>
-      <c r="M991" s="7"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I991">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I990">
       <formula1>"接纳,拒绝,重复,已实现"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G991">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G990">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
   </dataValidations>
@@ -15895,20 +15874,46 @@
         <v>42050</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
+    <row r="6" spans="1:13" ht="108">
+      <c r="A6" s="2">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="10">
+        <v>41983</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="K6" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="L6" s="7">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="M6" s="13">
+        <v>42050</v>
+      </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="2"/>
@@ -30640,6 +30645,7 @@
     <hyperlink ref="K3" r:id="rId2"/>
     <hyperlink ref="K4" r:id="rId3"/>
     <hyperlink ref="K5" r:id="rId4"/>
+    <hyperlink ref="K6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
+++ b/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="56">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -229,6 +229,26 @@
     <t xml:space="preserve">SEQUOIADBMAINSTREAM-578 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>update增加一个替换文档的功能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>论坛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>林友滨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>需求提交</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户需要根据条件将整个文档进行替换，多余的字段也不要，类似mongo的update里的replace document功能(lixiran)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -415,6 +435,74 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -426,7 +514,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="C7EDCC"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -15915,15 +16003,29 @@
         <v>42050</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
+    <row r="7" spans="1:13" ht="40.5">
+      <c r="A7" s="2">
+        <v>9</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" s="10">
+        <v>42072</v>
+      </c>
       <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
+      <c r="H7" s="2" t="s">
+        <v>54</v>
+      </c>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>

--- a/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
+++ b/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="58">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -246,7 +246,16 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>用户需要根据条件将整个文档进行替换，多余的字段也不要，类似mongo的update里的replace document功能(lixiran)</t>
+    <t xml:space="preserve">SEQUOIADBMAINSTREAM-629 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5人天</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">用户需要根据条件将整个文档进行替换，多余的字段也不要，类似mongo的update里的replace document功能(lixiran)
+</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -435,74 +444,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -514,7 +455,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="C7EDCC"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -16003,7 +15944,7 @@
         <v>42050</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="40.5">
+    <row r="7" spans="1:13" ht="54">
       <c r="A7" s="2">
         <v>9</v>
       </c>
@@ -16011,7 +15952,7 @@
         <v>51</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>52</v>
@@ -16022,15 +15963,27 @@
       <c r="F7" s="10">
         <v>42072</v>
       </c>
-      <c r="G7" s="2"/>
+      <c r="G7" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="H7" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
+      <c r="I7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="L7" s="7">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="M7" s="13">
+        <v>42088</v>
+      </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="2"/>
@@ -30748,6 +30701,7 @@
     <hyperlink ref="K4" r:id="rId3"/>
     <hyperlink ref="K5" r:id="rId4"/>
     <hyperlink ref="K6" r:id="rId5"/>
+    <hyperlink ref="K7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
+++ b/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="2014年" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="63">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -256,6 +256,26 @@
   <si>
     <t xml:space="preserve">用户需要根据条件将整个文档进行替换，多余的字段也不要，类似mongo的update里的replace document功能(lixiran)
 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdbadmin用户环境变量配置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>由于日后需要集成很多其他第三方模块进入企业版，因此统一运行环境越发重要。例如我们尽管在安装报里面自带了java_jdk，但是一些模块在使用的时候是使用绝对路径的，譬如在编译sample程序的时候使用的是相对于sample的路径。这里应当在安装的时候创建或更新用户的.bash_profile或.profile路径，增加相应的JAVA_HOME，而在各种脚本中则应优先使用环境变量而不是相对路径。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>王涛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>为集成spark作准备</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -881,15 +901,29 @@
       <c r="L4" s="7"/>
       <c r="M4" s="7"/>
     </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
+    <row r="5" spans="1:13" ht="135">
+      <c r="A5" s="2">
+        <v>10</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>59</v>
+      </c>
       <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
+      <c r="E5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" s="10">
+        <v>42077</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>62</v>
+      </c>
       <c r="I5" s="7"/>
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>

--- a/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
+++ b/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
@@ -4,19 +4,19 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="2014年" sheetId="1" r:id="rId1"/>
     <sheet name="已接纳" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="2015" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="77">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -278,6 +278,68 @@
     <t>为集成spark作准备</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>陈子川</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OM 在安装SequoiaDB软件时，一定需要用到root用户，这个针对企业用户不大合理。
+建议安装时，是要使用sudo user用户即可，并且让用户保证sudo user 在使用sudo 时，免密码操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在民生中，因为管理员并不知道每台机器的root密码，而且每台机器的root 密码都是不同的（他们使用root用户是由一个跳转软件实现）。
+但是他们有办法搞一个sudo user ，可以实现免输入密码执行sudo 命令。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OM在配置机器集群结构时，希望可以增加一个借口，让用户自己写好一个配置文件，直接进行导入。
+而不是在一大堆机器列表中，选择每个数据组中究竟有什么节点。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>民生生产环境部署时，我发现，如果机器数目、磁盘数目一旦上了规模，在选择每个数据组中有哪些节点时，这个过程反倒变得繁琐，而且用户很容易操作错误，时候也不容易发觉。
+如果可以让用户自己来填写部署结构，然后直接导入到OM中，这样用户就可以有一个完整的配置文件。
+之后重新部署、和事后归档文件，都是比较方便的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OM中增加监控数据库运行状态，例如数据库的读写状态、节点健康状态，异常报警等。
+并且增加接口，允许用户将这个状态信息导出文档，方便用户对接他们自身的监控系统</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>传统企业对于运维是十分关注的，监控底层数据库状态，这个必不可少。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>民生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>导入工具在字段切分上，目前只支持单个字符。希望未来增加多字符切分字段功能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加sequoaidb 的应急手册</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>企业在使用sequoiadb 过程中，不可避免会遇到一些特殊情况。例如已经上生产的系统突然异常了，用户应该可以根据一份应急手册，排查问题，并且解决</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户可以通过导入工具，使得从传统数据库中查询到数据 不需要落地，即可导入到sdb中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>导入工具新增流数据导入功能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -416,7 +478,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -455,6 +517,13 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -30743,9 +30812,181 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="78.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="198" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="27.75" thickBot="1">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="40.5">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F2" s="14">
+        <v>42083</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="40.5">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F3" s="14">
+        <v>42083</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="27">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="14">
+        <v>42083</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F5" s="14">
+        <v>42083</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F6" s="14">
+        <v>42083</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D7" t="s">
+        <v>70</v>
+      </c>
+      <c r="E7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F7" s="14">
+        <v>42083</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="B8" s="16"/>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="B9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
+++ b/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="82">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -353,6 +353,29 @@
   <si>
     <t xml:space="preserve">用户可以通过导入工具，使得从传统数据库中查询到数据 不需要落地，即可导入到sdb中
 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update/upsert 更新符增加字段追加功能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>途牛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陈子川</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果原来记录为
+{info:{id:1}} 
+现在希望通过update操作，在info 字段下的obj 里增加几个字段，变成
+{info:{id:1,age:23,name:"chen"}}
+目前，我们只能通过
+db.foo.bar.update({$set:{"info.age":23,"info.name":"chen"}})
+他们就希望有这么一个更新符，来做这个事情
+db.foo.bar.update($updateObj:{info:{name:"chen",age:23}})</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -846,7 +869,7 @@
   <cols>
     <col min="1" max="1" width="5.25" customWidth="1"/>
     <col min="2" max="2" width="32.375" customWidth="1"/>
-    <col min="3" max="3" width="36" customWidth="1"/>
+    <col min="3" max="3" width="41.25" customWidth="1"/>
     <col min="4" max="4" width="9.5" customWidth="1"/>
     <col min="5" max="5" width="8.875" customWidth="1"/>
     <col min="6" max="6" width="11.25" customWidth="1"/>
@@ -1151,13 +1174,25 @@
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
     </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
+    <row r="11" spans="1:13" ht="162">
+      <c r="A11" s="1">
+        <v>17</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F11" s="6">
+        <v>42090</v>
+      </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="5"/>
@@ -1172,7 +1207,7 @@
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
+      <c r="F12" s="6"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="5"/>

--- a/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
+++ b/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="86">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -376,6 +376,24 @@
 db.foo.bar.update({$set:{"info.age":23,"info.name":"chen"}})
 他们就希望有这么一个更新符，来做这个事情
 db.foo.bar.update($updateObj:{info:{name:"chen",age:23}})</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目前，如果用户想了解一个数据组中，各个数据节点的LSN号，以判断各个节点的同步状态，只能通过直接连接到每个数据节点去查看快照信息。
+这个操作对于用户来说，是在太繁琐了。
+建议在coord 中增加一个新的方法，让用户可以通过某个命令，可以在coord中查看到数据组中的各个数据节点的相关信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coord节点增加新方法，方便用户查看数据组中的各个数据节点状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>民生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陈子川</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -979,7 +997,7 @@
       <c r="L3" s="5"/>
       <c r="M3" s="5"/>
     </row>
-    <row r="4" spans="1:13" ht="148.5">
+    <row r="4" spans="1:13" ht="135">
       <c r="A4" s="1">
         <v>10</v>
       </c>
@@ -1037,7 +1055,7 @@
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
     </row>
-    <row r="6" spans="1:13" ht="148.5">
+    <row r="6" spans="1:13" ht="135">
       <c r="A6" s="1">
         <v>12</v>
       </c>
@@ -1147,7 +1165,7 @@
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
     </row>
-    <row r="10" spans="1:13" ht="54">
+    <row r="10" spans="1:13" ht="40.5">
       <c r="A10" s="1">
         <v>16</v>
       </c>
@@ -1201,13 +1219,25 @@
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
     </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="6"/>
+    <row r="12" spans="1:13" ht="94.5">
+      <c r="A12" s="1">
+        <v>18</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F12" s="6">
+        <v>42094</v>
+      </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="5"/>

--- a/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
+++ b/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="91">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -394,6 +394,26 @@
   </si>
   <si>
     <t>陈子川</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果用户指定多个协调节点，不要每次都连第一个，而是从列表中随机选择一个。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主子表优先从最新attach的子表开始查找</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>并发读线程增加反倒降低整体吞吐量，每小时1200-1800万，每条记录8k</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>将指定集合固定到内存</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>upsert返回更新和插入的数据条数</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1246,9 +1266,13 @@
       <c r="L12" s="5"/>
       <c r="M12" s="5"/>
     </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
+    <row r="13" spans="1:13" ht="40.5">
+      <c r="A13" s="1">
+        <v>19</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>86</v>
+      </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
@@ -1261,9 +1285,13 @@
       <c r="L13" s="5"/>
       <c r="M13" s="5"/>
     </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
+    <row r="14" spans="1:13" ht="27">
+      <c r="A14" s="1">
+        <v>20</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
@@ -1276,9 +1304,13 @@
       <c r="L14" s="5"/>
       <c r="M14" s="5"/>
     </row>
-    <row r="15" spans="1:13">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
+    <row r="15" spans="1:13" ht="27">
+      <c r="A15" s="1">
+        <v>21</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>88</v>
+      </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
@@ -1292,8 +1324,12 @@
       <c r="M15" s="5"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
+      <c r="A16" s="1">
+        <v>22</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>89</v>
+      </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
@@ -1307,8 +1343,12 @@
       <c r="M16" s="5"/>
     </row>
     <row r="17" spans="1:13">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
+      <c r="A17" s="1">
+        <v>23</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>90</v>
+      </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>

--- a/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
+++ b/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="2015年" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="96">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -115,10 +115,6 @@
     <t>中</t>
   </si>
   <si>
-    <t>正在分析</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">福建移动5台物理机（8核4线程，36磁盘，64G内存），一共36*5=180数据节点；业务为日志分析，导数日志400G花费1.5小时，数据节点CPU达到100%。业务采用主子表，每小时建1个子表，上层业务定期对子表进行计算，不存在update/delete操作；经测试，去除OID索引，性能可以提升一倍。
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -155,10 +151,6 @@
   </si>
   <si>
     <t>陈子川</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>提交jira单</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -229,10 +221,6 @@
   </si>
   <si>
     <t>林友滨</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>需求提交</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -397,23 +385,60 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>如果用户指定多个协调节点，不要每次都连第一个，而是从列表中随机选择一个。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>主子表优先从最新attach的子表开始查找</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>并发读线程增加反倒降低整体吞吐量，每小时1200-1800万，每条记录8k</t>
+    <t>王涛</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>将指定集合固定到内存</t>
+    <t>多盟</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>upsert返回更新和插入的数据条数</t>
+    <t xml:space="preserve">多盟采用主子表的场景是：每小时一个子表，保持24个子表，过期删除最老的子表；在导入数据的同时，会进行查询，查询是按OID匹配，采用findOne的方式。 我们现在是按Bound排序对子表进行查询，这样会从最老的子表开始查，速度很慢；如果反过来，从最新的子表开始查询，就会很快。
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已开发，提交测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SEQUOIADBMAINSTREAM-772 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.12.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">将指定集合固定到内存
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">upsert返回更新和插入的数据条数
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">如果用户指定多个协调节点，不要每次都连第一个，而是从列表中随机选择一个。
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">并发读线程增加反倒降低整体吞吐量，每小时1200-1800万，每条记录8k
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已完成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>接纳</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -902,7 +927,7 @@
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="A1:M989"/>
+  <dimension ref="A1:M988"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.25" customWidth="1"/>
@@ -966,14 +991,14 @@
         <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F2" s="6">
         <v>41982</v>
@@ -993,22 +1018,22 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F3" s="6">
         <v>41982</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="5"/>
@@ -1022,23 +1047,23 @@
         <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F4" s="6">
         <v>42077</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
@@ -1051,16 +1076,16 @@
         <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F5" s="6">
         <v>42083</v>
@@ -1080,16 +1105,16 @@
         <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F6" s="6">
         <v>42083</v>
@@ -1109,16 +1134,16 @@
         <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F7" s="6">
         <v>42083</v>
@@ -1138,14 +1163,14 @@
         <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F8" s="6">
         <v>42083</v>
@@ -1163,16 +1188,16 @@
         <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F9" s="6">
         <v>42083</v>
@@ -1190,16 +1215,16 @@
         <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F10" s="6">
         <v>42083</v>
@@ -1217,16 +1242,16 @@
         <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="D11" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F11" s="6">
         <v>42090</v>
@@ -1244,16 +1269,16 @@
         <v>18</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F12" s="6">
         <v>42094</v>
@@ -1266,17 +1291,23 @@
       <c r="L12" s="5"/>
       <c r="M12" s="5"/>
     </row>
-    <row r="13" spans="1:13" ht="40.5">
+    <row r="13" spans="1:13" ht="54">
       <c r="A13" s="1">
         <v>19</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
+      <c r="D13" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="6">
+        <v>42094</v>
+      </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="5"/>
@@ -1285,17 +1316,23 @@
       <c r="L13" s="5"/>
       <c r="M13" s="5"/>
     </row>
-    <row r="14" spans="1:13" ht="27">
+    <row r="14" spans="1:13" ht="40.5">
       <c r="A14" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
+      <c r="D14" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F14" s="6">
+        <v>42094</v>
+      </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="5"/>
@@ -1306,15 +1343,21 @@
     </row>
     <row r="15" spans="1:13" ht="27">
       <c r="A15" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
+      <c r="D15" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F15" s="6">
+        <v>42094</v>
+      </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="5"/>
@@ -1323,17 +1366,23 @@
       <c r="L15" s="5"/>
       <c r="M15" s="5"/>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:13" ht="27">
       <c r="A16" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
+      <c r="D16" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F16" s="6">
+        <v>42094</v>
+      </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="5"/>
@@ -1343,12 +1392,8 @@
       <c r="M16" s="5"/>
     </row>
     <row r="17" spans="1:13">
-      <c r="A17" s="1">
-        <v>23</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>90</v>
-      </c>
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
@@ -15926,28 +15971,13 @@
       <c r="L988" s="5"/>
       <c r="M988" s="5"/>
     </row>
-    <row r="989" spans="1:13">
-      <c r="A989" s="1"/>
-      <c r="B989" s="1"/>
-      <c r="C989" s="1"/>
-      <c r="D989" s="1"/>
-      <c r="E989" s="1"/>
-      <c r="F989" s="1"/>
-      <c r="G989" s="1"/>
-      <c r="H989" s="1"/>
-      <c r="I989" s="5"/>
-      <c r="J989" s="5"/>
-      <c r="K989" s="5"/>
-      <c r="L989" s="5"/>
-      <c r="M989" s="5"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I989">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I988">
       <formula1>"接纳,拒绝,重复,已实现"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G989">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G988">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
   </dataValidations>
@@ -16047,10 +16077,10 @@
         <v>19</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M2" s="10">
         <v>41986</v>
@@ -16061,14 +16091,14 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C3" s="12"/>
       <c r="D3" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F3" s="13">
         <v>41982</v>
@@ -16077,16 +16107,16 @@
         <v>23</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="K3" s="14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="L3" s="12">
         <v>1.1200000000000001</v>
@@ -16100,14 +16130,14 @@
         <v>6</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C4" s="12"/>
       <c r="D4" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F4" s="13">
         <v>41982</v>
@@ -16116,16 +16146,16 @@
         <v>23</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>34</v>
+        <v>94</v>
       </c>
       <c r="I4" s="12" t="s">
         <v>12</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L4" s="12">
         <v>1.1200000000000001</v>
@@ -16139,14 +16169,14 @@
         <v>8</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C5" s="12"/>
       <c r="D5" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F5" s="13">
         <v>41982</v>
@@ -16155,16 +16185,16 @@
         <v>23</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>34</v>
+        <v>94</v>
       </c>
       <c r="I5" s="12" t="s">
         <v>12</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L5" s="12">
         <v>1.1200000000000001</v>
@@ -16181,7 +16211,7 @@
         <v>20</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>21</v>
@@ -16196,16 +16226,16 @@
         <v>23</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="I6" s="12" t="s">
         <v>12</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K6" s="14" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L6" s="12">
         <v>1.1200000000000001</v>
@@ -16215,43 +16245,43 @@
       </c>
     </row>
     <row r="7" spans="1:13" ht="54">
-      <c r="A7" s="1">
+      <c r="A7" s="12">
         <v>9</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="F7" s="13">
+        <v>42072</v>
+      </c>
+      <c r="G7" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="H7" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K7" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F7" s="6">
-        <v>42072</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="L7" s="5">
+      <c r="L7" s="12">
         <v>1.1399999999999999</v>
       </c>
-      <c r="M7" s="8">
+      <c r="M7" s="13">
         <v>42088</v>
       </c>
     </row>
@@ -16260,14 +16290,14 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F8" s="6">
         <v>41981</v>
@@ -16276,13 +16306,13 @@
         <v>23</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>12</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="K8" s="5"/>
       <c r="L8" s="5">
@@ -16290,20 +16320,46 @@
       </c>
       <c r="M8" s="5"/>
     </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
+    <row r="9" spans="1:13" ht="121.5">
+      <c r="A9" s="1">
+        <v>20</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F9" s="6">
+        <v>42094</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J9" s="5">
+        <v>3</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="M9" s="8">
+        <v>42097</v>
+      </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="1"/>
@@ -30992,8 +31048,9 @@
     <hyperlink ref="K5" r:id="rId4"/>
     <hyperlink ref="K6" r:id="rId5"/>
     <hyperlink ref="K7" r:id="rId6"/>
+    <hyperlink ref="K9" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId8"/>
 </worksheet>
 </file>
--- a/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
+++ b/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="2015年" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="103">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -439,6 +439,35 @@
   </si>
   <si>
     <t>接纳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在福州移动中，原始数据经过处理后，得到一个目标数据集，用户需要根据这些目标数据集做group by的操作，用来向前端展现最后的结果。目前由于我们没有将group by 操作下压，导致性能不够理想</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>福州移动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陈子川</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdb 的domain 功能，增加一个autoBalance 的功能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>民生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdb 的aggregate 方法，将group by 功能下压到子节点中执行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户在使用domain功能时，希望它能自动平衡数据切分的功能。
+例如在开始时，是由3个数据组构成的domain1，后面用户新增了group4、group5、group6 三个数据组到domain1 中，用户希望能有一个命令，将全量数据集平衡到6 个数据组中</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1391,13 +1420,25 @@
       <c r="L16" s="5"/>
       <c r="M16" s="5"/>
     </row>
-    <row r="17" spans="1:13">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
+    <row r="17" spans="1:13" ht="67.5">
+      <c r="A17" s="1">
+        <v>24</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F17" s="6">
+        <v>42102</v>
+      </c>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="5"/>
@@ -1406,13 +1447,25 @@
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
     </row>
-    <row r="18" spans="1:13">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
+    <row r="18" spans="1:13" ht="81">
+      <c r="A18" s="1">
+        <v>25</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F18" s="6">
+        <v>42102</v>
+      </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="5"/>

--- a/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
+++ b/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="107">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -468,6 +468,22 @@
   <si>
     <t>用户在使用domain功能时，希望它能自动平衡数据切分的功能。
 例如在开始时，是由3个数据组构成的domain1，后面用户新增了group4、group5、group6 三个数据组到domain1 中，用户希望能有一个命令，将全量数据集平衡到6 个数据组中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加一个全量导入导出工具</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当sdb 中存在多个cl时，如果用户希望将所有数据导出，并且迁移到其他机器中做恢复工作，由于目前sdb 的导入和导出工具都是针对cl 的，并没有一个有效的工具能完成整个数据库数据的导入、导出，所以需要用户自己编写脚本完成这项工作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>天津中行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陈子川</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1474,13 +1490,25 @@
       <c r="L18" s="5"/>
       <c r="M18" s="5"/>
     </row>
-    <row r="19" spans="1:13">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
+    <row r="19" spans="1:13" ht="81">
+      <c r="A19" s="1">
+        <v>26</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F19" s="6">
+        <v>42104</v>
+      </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="5"/>

--- a/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
+++ b/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="129">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -484,6 +484,94 @@
   </si>
   <si>
     <t>陈子川</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>驱动连接多个coord做路由，建议调整为从catalog 获取存活coord节点信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目前由于catalog并没有存储所有coord信息，导致驱动需要连接多个coord时，需要手工填写多个coord列表，并且这种方式对于未来新增coord节点后，应用服务也需要同时调整代码或者配置文件，非常不方便。参考hadoop相关控件的做法，一般是由一个像catalog的服务来提供所有master信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>民生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陈子川</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ReplSize=0 时，当其中一个节点宕机，动态调整写入成功数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果用户希望数据一致性级别调整为最高，ReplSize=0时，目前我们只是简单调整为数据组的节点数。一旦一个节点宕机，数据组中其实还是可以正常选出主节点来，但是这时候数据应该不可能写入成功了，这个对于应用来说是合理的。建议增加一个选项，让数据能在存活节点上全部写入成功再给应用返回失败</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主子表使用上，目前子表attach上主表后，在listCollections中隐藏子表的信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一般使用主子表的场景里都是历史数据归档，所涉及的子表会非常多，而且一旦介入的项目增加，子表的数目会成倍数增长。目前在民生中就遇到这样的问题，用户一个主表中attach 了大量的子表，在listCollections 时，所有的主子表信息都会打印在屏幕上，用户根本无法快速获取有用信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdbimprt工具增加多线程导入</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果用户针对一个特别大的文件做数据导入时，使用sdbimprt 来做导入，目前只有单个线程工作，导入效率不高，能否给sdbimprt 工具增加一个多线程的导入的功能，提升导入效率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdbimprt工具增加导入文件夹功能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果用户有一个文件夹的数据需要导入到sdb 中，由于sdbimprt 没有导入整个文件夹的功能，用户只能通过编写一个shell 脚本来循环导入 ，效率不高</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据被切分后，支持数据自动均衡的功能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">如果用户在使用domain 或者split 根据某个字段做了hash 切分，但是由于目标数据可能发生了倾斜，在应用系统运行后期，会发生数据倾斜的问题，建议我们sdb 引擎中增加数据自平衡的功能，方便DBA管理sdb </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>domain 新增数据组后，原有数据并不能被打散到新数据组中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>应用开始时使用domain给cl 做了hash 切分，但是在一段时间后，sdb 集群得到了扩展，相应domain也同步调整为新的集群，但是原有依赖此domain的表并不能自动均衡到新的数据组中，还需要DBA手工计算，将不同的分片切分到新数据组中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加从关系型数据库迁移到sdb 的工具</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目前使用sdb 的主要场景都是历史数据平台。此平台的建设有一个特点，需要将数据从原关系型数据库中导入到sdb中。目前由于我们没有这种迁移工具，一个项目实施，就需要集成商开发一次，开发成本较高，并且由于他们对于sdb 的特性不熟悉，往往会有很多的性能调优的工作需要我们帮助</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加查看数据导入后的存储位置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在我们使用了hash 给cl 做了切分后，数据导入时，我们并不清楚这份数据是被存储在哪个分片中，在一些异常状况发生时，用户需要手工确认一下某些数据是否被真实写入到指定的分片中，这时候，他们就需要一个新方法，来查看这份数据应该被存储在哪个分片上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>postgresql 支持更多的数据类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在pg比价完美支持的类型就只有text/numeric/bool 等，但是这些类型，在一般关系型数据库中并不常见，像string ，用户一般会使用varchar（200）之类的类型来定义。而用户使用pg 来对接sdb时，往往是将旧表原封不动地迁移到sdb中，给pg 建立映射表时，同样也会拿原来的建表语句拷贝过来在pg中执行。如果迁移的表都需要重新调整字段类型，一旦迁移的表增加，工作量会大大增加，而且很容易出错</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1517,13 +1605,25 @@
       <c r="L19" s="5"/>
       <c r="M19" s="5"/>
     </row>
-    <row r="20" spans="1:13">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
+    <row r="20" spans="1:13" ht="94.5">
+      <c r="A20" s="1">
+        <v>27</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F20" s="6">
+        <v>42124</v>
+      </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="5"/>
@@ -1532,13 +1632,25 @@
       <c r="L20" s="5"/>
       <c r="M20" s="5"/>
     </row>
-    <row r="21" spans="1:13">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
+    <row r="21" spans="1:13" ht="94.5">
+      <c r="A21" s="1">
+        <v>28</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F21" s="6">
+        <v>42124</v>
+      </c>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="5"/>
@@ -1547,13 +1659,25 @@
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
     </row>
-    <row r="22" spans="1:13">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
+    <row r="22" spans="1:13" ht="94.5">
+      <c r="A22" s="1">
+        <v>29</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F22" s="6">
+        <v>42124</v>
+      </c>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="5"/>
@@ -1562,13 +1686,25 @@
       <c r="L22" s="5"/>
       <c r="M22" s="5"/>
     </row>
-    <row r="23" spans="1:13">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
+    <row r="23" spans="1:13" ht="54">
+      <c r="A23" s="1">
+        <v>30</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F23" s="6">
+        <v>42124</v>
+      </c>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="5"/>
@@ -1577,13 +1713,25 @@
       <c r="L23" s="5"/>
       <c r="M23" s="5"/>
     </row>
-    <row r="24" spans="1:13">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
+    <row r="24" spans="1:13" ht="54">
+      <c r="A24" s="1">
+        <v>31</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F24" s="6">
+        <v>42124</v>
+      </c>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="5"/>
@@ -1592,13 +1740,25 @@
       <c r="L24" s="5"/>
       <c r="M24" s="5"/>
     </row>
-    <row r="25" spans="1:13">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
+    <row r="25" spans="1:13" ht="67.5">
+      <c r="A25" s="1">
+        <v>32</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F25" s="6">
+        <v>42124</v>
+      </c>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="5"/>
@@ -1607,13 +1767,25 @@
       <c r="L25" s="5"/>
       <c r="M25" s="5"/>
     </row>
-    <row r="26" spans="1:13">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
+    <row r="26" spans="1:13" ht="81">
+      <c r="A26" s="1">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F26" s="6">
+        <v>42124</v>
+      </c>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="5"/>
@@ -1622,13 +1794,25 @@
       <c r="L26" s="5"/>
       <c r="M26" s="5"/>
     </row>
-    <row r="27" spans="1:13">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
+    <row r="27" spans="1:13" ht="94.5">
+      <c r="A27" s="1">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F27" s="6">
+        <v>42124</v>
+      </c>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="5"/>
@@ -1637,13 +1821,25 @@
       <c r="L27" s="5"/>
       <c r="M27" s="5"/>
     </row>
-    <row r="28" spans="1:13">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
+    <row r="28" spans="1:13" ht="81">
+      <c r="A28" s="1">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F28" s="6">
+        <v>42124</v>
+      </c>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="5"/>
@@ -1652,13 +1848,25 @@
       <c r="L28" s="5"/>
       <c r="M28" s="5"/>
     </row>
-    <row r="29" spans="1:13">
-      <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
+    <row r="29" spans="1:13" ht="121.5">
+      <c r="A29" s="1">
+        <v>36</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F29" s="6">
+        <v>42124</v>
+      </c>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="5"/>

--- a/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
+++ b/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="132">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -574,6 +574,18 @@
     <t>现在pg比价完美支持的类型就只有text/numeric/bool 等，但是这些类型，在一般关系型数据库中并不常见，像string ，用户一般会使用varchar（200）之类的类型来定义。而用户使用pg 来对接sdb时，往往是将旧表原封不动地迁移到sdb中，给pg 建立映射表时，同样也会拿原来的建表语句拷贝过来在pg中执行。如果迁移的表都需要重新调整字段类型，一旦迁移的表增加，工作量会大大增加，而且很容易出错</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>db.cs.cl.remove()操作支持数据强一致性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目前，如果在建立cl 时，没有指定ReplSize，那么sdb默认是只删除了主节点数据就给应用返回成功，但是在生产环境中，某些场景里，需要在ReplSize = 1 时，用户操作remove，需要确定一个数据组3个节点都已经完成cl 清空。现在的方法是不断的count，但是这个方法太麻烦了。建议给remove 增加一个参数，实现数据节点之间的数据强一致性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>民生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1875,13 +1887,25 @@
       <c r="L29" s="5"/>
       <c r="M29" s="5"/>
     </row>
-    <row r="30" spans="1:13">
-      <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
+    <row r="30" spans="1:13" ht="108">
+      <c r="A30" s="1">
+        <v>37</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F30" s="6">
+        <v>42124</v>
+      </c>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="5"/>

--- a/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
+++ b/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="2015年" sheetId="1" r:id="rId1"/>
@@ -274,12 +274,6 @@
   </si>
   <si>
     <t>陈子川</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">OM在配置机器集群结构时，希望可以增加一个借口，让用户自己写好一个配置文件，直接进行导入。
-而不是在一大堆机器列表中，选择每个数据组中究竟有什么节点。
-</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -584,6 +578,12 @@
   </si>
   <si>
     <t>民生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">OM在配置机器集群结构时，希望可以增加一个接口，让用户自己写好一个配置文件，直接进行导入。
+而不是在一大堆机器列表中，选择每个数据组中究竟有什么节点。
+</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1166,7 +1166,7 @@
         <v>38</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>31</v>
@@ -1195,7 +1195,7 @@
         <v>53</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1" t="s">
@@ -1250,10 +1250,10 @@
         <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>62</v>
+        <v>131</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>60</v>
@@ -1279,10 +1279,10 @@
         <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>60</v>
@@ -1308,7 +1308,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
@@ -1333,10 +1333,10 @@
         <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>60</v>
@@ -1360,10 +1360,10 @@
         <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>60</v>
@@ -1387,16 +1387,16 @@
         <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D11" s="1" t="s">
+      <c r="E11" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>77</v>
       </c>
       <c r="F11" s="6">
         <v>42090</v>
@@ -1414,16 +1414,16 @@
         <v>18</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D12" s="1" t="s">
+      <c r="E12" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>82</v>
       </c>
       <c r="F12" s="6">
         <v>42094</v>
@@ -1441,11 +1441,11 @@
         <v>19</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>26</v>
@@ -1466,14 +1466,14 @@
         <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F14" s="6">
         <v>42094</v>
@@ -1491,14 +1491,14 @@
         <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F15" s="6">
         <v>42094</v>
@@ -1516,14 +1516,14 @@
         <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F16" s="6">
         <v>42094</v>
@@ -1541,16 +1541,16 @@
         <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="E17" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="F17" s="6">
         <v>42102</v>
@@ -1568,16 +1568,16 @@
         <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>100</v>
-      </c>
       <c r="E18" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F18" s="6">
         <v>42102</v>
@@ -1595,16 +1595,16 @@
         <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="D19" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="E19" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="F19" s="6">
         <v>42104</v>
@@ -1622,16 +1622,16 @@
         <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="D20" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="E20" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>110</v>
       </c>
       <c r="F20" s="6">
         <v>42124</v>
@@ -1649,16 +1649,16 @@
         <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>112</v>
-      </c>
       <c r="D21" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F21" s="6">
         <v>42124</v>
@@ -1676,16 +1676,16 @@
         <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>114</v>
-      </c>
       <c r="D22" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F22" s="6">
         <v>42124</v>
@@ -1703,16 +1703,16 @@
         <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>116</v>
-      </c>
       <c r="D23" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F23" s="6">
         <v>42124</v>
@@ -1730,16 +1730,16 @@
         <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>118</v>
-      </c>
       <c r="D24" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F24" s="6">
         <v>42124</v>
@@ -1757,16 +1757,16 @@
         <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>120</v>
-      </c>
       <c r="D25" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F25" s="6">
         <v>42124</v>
@@ -1784,16 +1784,16 @@
         <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>122</v>
-      </c>
       <c r="D26" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F26" s="6">
         <v>42124</v>
@@ -1811,16 +1811,16 @@
         <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>124</v>
-      </c>
       <c r="D27" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F27" s="6">
         <v>42124</v>
@@ -1838,16 +1838,16 @@
         <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>126</v>
-      </c>
       <c r="D28" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F28" s="6">
         <v>42124</v>
@@ -1865,16 +1865,16 @@
         <v>36</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>128</v>
-      </c>
       <c r="D29" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F29" s="6">
         <v>42124</v>
@@ -1892,13 +1892,13 @@
         <v>37</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="D30" s="1" t="s">
         <v>130</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>131</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>57</v>
@@ -16459,7 +16459,7 @@
         <v>23</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I4" s="12" t="s">
         <v>12</v>
@@ -16498,7 +16498,7 @@
         <v>23</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I5" s="12" t="s">
         <v>12</v>
@@ -16539,7 +16539,7 @@
         <v>23</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I6" s="12" t="s">
         <v>12</v>
@@ -16580,10 +16580,10 @@
         <v>55</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J7" s="12" t="s">
         <v>51</v>
@@ -16619,13 +16619,13 @@
         <v>23</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>12</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K8" s="5"/>
       <c r="L8" s="5">
@@ -16638,16 +16638,16 @@
         <v>20</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F9" s="6">
         <v>42094</v>
@@ -16656,7 +16656,7 @@
         <v>16</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>12</v>
@@ -16665,10 +16665,10 @@
         <v>3</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M9" s="8">
         <v>42097</v>

--- a/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
+++ b/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="2015年" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="136">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -586,6 +586,25 @@
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>监控节点使用的磁盘健康状况</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>之前我们在民生的一个项目，使用sdb集群方式部署。系统运行一段时间后，一块磁盘意外崩溃，但是由于他们的DBA没有经常检查硬件状况，我们sdb 也没有报告相关的错误，导致这个问题持续了几个月才被发现。
+经过了解，如果当节点在运行过程中，磁盘突然损坏或者被强行unmout ，我们的节点是不会产生任何错误信息，只是之后的所有读写操作都失败。
+这个情况对于数据安全保障存在一定的隐患，由于我们没有一种有效的检测机制，用户很有可能就会忽略这个异常的存在。当一个组三节点中的两个节点因为磁盘损坏没有同步数据，当主节点宕机后，整个系统处于崩溃状态。
+希望我们在后面加强这方面的监控</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>民生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陈子川</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1914,13 +1933,25 @@
       <c r="L30" s="5"/>
       <c r="M30" s="5"/>
     </row>
-    <row r="31" spans="1:13">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
+    <row r="31" spans="1:13" ht="202.5">
+      <c r="A31" s="1">
+        <v>38</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F31" s="6">
+        <v>42143</v>
+      </c>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="5"/>

--- a/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
+++ b/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="138">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -605,6 +605,14 @@
     <t>陈子川</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>snapshot（3） 增加用户操作细节</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在DBA 运维过程中，如果遇到系统运行变慢，或者是某个应用运行变慢，需要从数据库定位变慢的原因，但是由于数据库运行应用非常多，DBA 很难通过查看应用的每个命令来定位问题，所以如果sdb 能在快照信息中，提供目前正在运行的执行命令，并且清楚描述正在做什么</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1960,13 +1968,25 @@
       <c r="L31" s="5"/>
       <c r="M31" s="5"/>
     </row>
-    <row r="32" spans="1:13">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
+    <row r="32" spans="1:13" ht="81">
+      <c r="A32" s="1">
+        <v>39</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F32" s="6">
+        <v>42149</v>
+      </c>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="5"/>

--- a/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
+++ b/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="138">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -396,10 +396,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>已开发，提交测试</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">SEQUOIADBMAINSTREAM-772 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -613,6 +609,10 @@
     <t>在DBA 运维过程中，如果遇到系统运行变慢，或者是某个应用运行变慢，需要从数据库定位变慢的原因，但是由于数据库运行应用非常多，DBA 很难通过查看应用的每个命令来定位问题，所以如果sdb 能在快照信息中，提供目前正在运行的执行命令，并且清楚描述正在做什么</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>已规划</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -757,7 +757,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -775,12 +775,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1277,7 +1271,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>62</v>
@@ -1468,7 +1462,7 @@
         <v>19</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1" t="s">
@@ -1480,9 +1474,15 @@
       <c r="F13" s="6">
         <v>42094</v>
       </c>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="5"/>
+      <c r="G13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>12</v>
+      </c>
       <c r="J13" s="5"/>
       <c r="K13" s="5"/>
       <c r="L13" s="5"/>
@@ -1493,7 +1493,7 @@
         <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1" t="s">
@@ -1518,7 +1518,7 @@
         <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1" t="s">
@@ -1543,7 +1543,7 @@
         <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1" t="s">
@@ -1568,16 +1568,16 @@
         <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="E17" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>97</v>
       </c>
       <c r="F17" s="6">
         <v>42102</v>
@@ -1595,16 +1595,16 @@
         <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>99</v>
-      </c>
       <c r="E18" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F18" s="6">
         <v>42102</v>
@@ -1622,16 +1622,16 @@
         <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="D19" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="E19" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>105</v>
       </c>
       <c r="F19" s="6">
         <v>42104</v>
@@ -1649,16 +1649,16 @@
         <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="D20" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="E20" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>109</v>
       </c>
       <c r="F20" s="6">
         <v>42124</v>
@@ -1676,16 +1676,16 @@
         <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>111</v>
-      </c>
       <c r="D21" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F21" s="6">
         <v>42124</v>
@@ -1703,16 +1703,16 @@
         <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>113</v>
-      </c>
       <c r="D22" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F22" s="6">
         <v>42124</v>
@@ -1730,16 +1730,16 @@
         <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>115</v>
-      </c>
       <c r="D23" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F23" s="6">
         <v>42124</v>
@@ -1757,16 +1757,16 @@
         <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="D24" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F24" s="6">
         <v>42124</v>
@@ -1784,16 +1784,16 @@
         <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>119</v>
-      </c>
       <c r="D25" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F25" s="6">
         <v>42124</v>
@@ -1811,16 +1811,16 @@
         <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="D26" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F26" s="6">
         <v>42124</v>
@@ -1838,16 +1838,16 @@
         <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>123</v>
-      </c>
       <c r="D27" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F27" s="6">
         <v>42124</v>
@@ -1865,16 +1865,16 @@
         <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>125</v>
-      </c>
       <c r="D28" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F28" s="6">
         <v>42124</v>
@@ -1892,16 +1892,16 @@
         <v>36</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="D29" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F29" s="6">
         <v>42124</v>
@@ -1919,13 +1919,13 @@
         <v>37</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="D30" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>130</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>57</v>
@@ -1946,16 +1946,16 @@
         <v>38</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="D31" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="E31" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>135</v>
       </c>
       <c r="F31" s="6">
         <v>42143</v>
@@ -1973,10 +1973,10 @@
         <v>39</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>60</v>
@@ -16412,240 +16412,240 @@
       </c>
     </row>
     <row r="2" spans="1:13" ht="94.5">
-      <c r="A2" s="9">
+      <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9" t="s">
+      <c r="C2" s="7"/>
+      <c r="D2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="8">
         <v>41981</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="K2" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="L2" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="M2" s="10">
+      <c r="M2" s="8">
         <v>41986</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="67.5">
-      <c r="A3" s="12">
+      <c r="A3" s="10">
         <v>4</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12" t="s">
+      <c r="C3" s="10"/>
+      <c r="D3" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="11">
         <v>41982</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="J3" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="K3" s="14" t="s">
+      <c r="K3" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="L3" s="12">
+      <c r="L3" s="10">
         <v>1.1200000000000001</v>
       </c>
-      <c r="M3" s="13">
+      <c r="M3" s="11">
         <v>42050</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="40.5">
-      <c r="A4" s="12">
+      <c r="A4" s="10">
         <v>6</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12" t="s">
+      <c r="C4" s="10"/>
+      <c r="D4" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="11">
         <v>41982</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="H4" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L4" s="10">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="M4" s="11">
+        <v>42050</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="40.5">
+      <c r="A5" s="10">
+        <v>8</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="11">
+        <v>41982</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="K5" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="L5" s="10">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="M5" s="11">
+        <v>42050</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="108">
+      <c r="A6" s="10">
+        <v>2</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="11">
+        <v>41983</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="J6" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="K6" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="L6" s="10">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="M6" s="11">
+        <v>42050</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="54">
+      <c r="A7" s="10">
+        <v>9</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="11">
+        <v>42072</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="I7" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="I4" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="J4" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="K4" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="L4" s="12">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="M4" s="13">
-        <v>42050</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="40.5">
-      <c r="A5" s="12">
-        <v>8</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" s="13">
-        <v>41982</v>
-      </c>
-      <c r="G5" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="I5" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="J5" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="K5" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="L5" s="12">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="M5" s="13">
-        <v>42050</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="108">
-      <c r="A6" s="12">
-        <v>2</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="13">
-        <v>41983</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="I6" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="K6" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="L6" s="12">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="M6" s="13">
-        <v>42050</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="54">
-      <c r="A7" s="12">
-        <v>9</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="F7" s="13">
-        <v>42072</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="H7" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="I7" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="J7" s="12" t="s">
+      <c r="J7" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="K7" s="14" t="s">
+      <c r="K7" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="L7" s="12">
+      <c r="L7" s="10">
         <v>1.1399999999999999</v>
       </c>
-      <c r="M7" s="13">
+      <c r="M7" s="11">
         <v>42088</v>
       </c>
     </row>
@@ -16685,43 +16685,43 @@
       <c r="M8" s="5"/>
     </row>
     <row r="9" spans="1:13" ht="121.5">
-      <c r="A9" s="1">
+      <c r="A9" s="10">
         <v>20</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="11">
         <v>42094</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="H9" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="J9" s="10">
+        <v>3</v>
+      </c>
+      <c r="K9" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="I9" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="J9" s="5">
-        <v>3</v>
-      </c>
-      <c r="K9" s="7" t="s">
+      <c r="L9" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="L9" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="M9" s="8">
+      <c r="M9" s="11">
         <v>42097</v>
       </c>
     </row>

--- a/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
+++ b/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="144">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -162,22 +162,12 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">sdbimprt导入工具字段分隔符需要支持多字符，降低重复几率
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">在官网上下载的driver包中，应该带上samples文件夹，方面开发者使用
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">SEQUOIADBMAINSTREAM-501 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">sdbimprt导入工具支持从管道导入数据（例如 sdbimprt --exec 'dbexprt xxxxx' 从执行的命令导入数据）
-</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -289,12 +279,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">用户在从db2等导入数据到sequoiadb时不需要让数据落地
-但需要考虑是否有其它的打印信息？
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>60人天</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -313,27 +297,12 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">导入工具在字段切分上，目前只支持单个字符。希望未来增加多字符切分字段功能
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">增加sequoaidb 的应急手册
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">企业在使用sequoiadb 过程中，不可避免会遇到一些特殊情况。例如已经上生产的系统突然异常了，用户应该可以根据一份应急手册，排查问题，并且解决
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">导入工具新增流数据导入功能
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">用户可以通过导入工具，使得从传统数据库中查询到数据 不需要落地，即可导入到sdb中
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -509,14 +478,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>sdbimprt工具增加多线程导入</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>如果用户针对一个特别大的文件做数据导入时，使用sdbimprt 来做导入，目前只有单个线程工作，导入效率不高，能否给sdbimprt 工具增加一个多线程的导入的功能，提升导入效率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>sdbimprt工具增加导入文件夹功能</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -611,6 +572,79 @@
   </si>
   <si>
     <t>已规划</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SEQUOIADBMAINSTREAM-948 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1、导入工具在导入大数据量（单个文件达到100G甚至T级）时，由于是单线程导入，性能极慢；
+2、导入工具对于大匹量导入数据失败时，不能有效认识出失败的数据；
+3、导入工具对分隔符的适配有限，多字符不支持；
+4、导入工具对字段类型格式转换支持不完善
+5、用户在从db2等导入数据到sequoiadb时不需要让数据落地
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">【性能】
+1、支持对大文件进行并发导入，性能达到10W/S
+【易用】
+1、支持多字段分隔符
+2、支持对导入失败的数据进行记录，并支持增量对失败数据进行导入
+3、支持导入的段点续传
+4、对各类型转换支持标准规则+自定义规则
+5、支持UTF-8(带BOM/无BOM）编码格式的数据源（GBXXXX优先级低）
+6、支持从管道导入数据（例如 sdbimprt XXXXXX --exec 'dbexprt xxxx'，或从一个查询语句导入数据）
+【兼容】
+1、参数兼容
+2、功能兼容
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已规划</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SEQUOIADBMAINSTREAM-825 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SEQUOIADBMAINSTREAM-913 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>考虑走现有的migrate脚本？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>和导入工具拉通考虑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>local(bson record)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现有pg类型分析，除多维数据不能支持，其它都支持</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SEQUOIADBMAINSTREAM-918 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这块放到监控中统一规则</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>待规划</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>和节点监控统一规则</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -757,7 +791,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -793,6 +827,15 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="58" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="58" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1093,7 +1136,7 @@
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="A1:M988"/>
+  <dimension ref="A1:M982"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.25" customWidth="1"/>
@@ -1152,16 +1195,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="40.5">
+    <row r="2" spans="1:13" ht="256.5">
       <c r="A2" s="1">
         <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C2" s="1"/>
+        <v>132</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="D2" s="1" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>32</v>
@@ -1170,66 +1215,80 @@
         <v>41982</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2" s="1"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-    </row>
-    <row r="3" spans="1:13" ht="67.5">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="5">
+        <v>20</v>
+      </c>
+      <c r="K2" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="L2" s="5">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="M2" s="13">
+        <v>42200</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="135">
       <c r="A3" s="1">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>31</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="D3" s="1"/>
       <c r="E3" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F3" s="6">
-        <v>41982</v>
+        <v>42077</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H3" s="1"/>
+        <v>53</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>54</v>
+      </c>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
       <c r="K3" s="5"/>
       <c r="L3" s="5"/>
       <c r="M3" s="5"/>
     </row>
-    <row r="4" spans="1:13" ht="135">
+    <row r="4" spans="1:13" ht="94.5">
       <c r="A4" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D4" s="1"/>
+        <v>57</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>58</v>
+      </c>
       <c r="E4" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F4" s="6">
-        <v>42077</v>
+        <v>42083</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>56</v>
+        <v>142</v>
       </c>
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
@@ -1237,21 +1296,21 @@
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
     </row>
-    <row r="5" spans="1:13" ht="94.5">
+    <row r="5" spans="1:13" ht="135">
       <c r="A5" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="F5" s="6">
         <v>42083</v>
@@ -1259,28 +1318,30 @@
       <c r="G5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H5" s="1"/>
+      <c r="H5" s="1" t="s">
+        <v>142</v>
+      </c>
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
     </row>
-    <row r="6" spans="1:13" ht="135">
+    <row r="6" spans="1:13" ht="94.5">
       <c r="A6" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>130</v>
+        <v>64</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F6" s="6">
         <v>42083</v>
@@ -1288,383 +1349,423 @@
       <c r="G6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H6" s="1"/>
+      <c r="H6" s="1" t="s">
+        <v>142</v>
+      </c>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
       <c r="M6" s="5"/>
     </row>
-    <row r="7" spans="1:13" ht="94.5">
+    <row r="7" spans="1:13" ht="67.5">
       <c r="A7" s="1">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>68</v>
-      </c>
       <c r="D7" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F7" s="6">
         <v>42083</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1" t="s">
+        <v>142</v>
+      </c>
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
       <c r="L7" s="5"/>
       <c r="M7" s="5"/>
     </row>
-    <row r="8" spans="1:13" ht="54">
+    <row r="8" spans="1:13" ht="162">
       <c r="A8" s="1">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="E8" s="1" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="F8" s="6">
-        <v>42083</v>
+        <v>42090</v>
       </c>
       <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
+      <c r="H8" s="1" t="s">
+        <v>142</v>
+      </c>
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
     </row>
-    <row r="9" spans="1:13" ht="67.5">
+    <row r="9" spans="1:13" ht="94.5">
       <c r="A9" s="1">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="F9" s="6">
-        <v>42083</v>
-      </c>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
+        <v>42094</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>143</v>
+      </c>
       <c r="I9" s="5"/>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
     </row>
-    <row r="10" spans="1:13" ht="40.5">
+    <row r="10" spans="1:13" ht="54">
       <c r="A10" s="1">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>73</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="F10" s="6">
-        <v>42083</v>
-      </c>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="5"/>
+        <v>42094</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>12</v>
+      </c>
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
     </row>
-    <row r="11" spans="1:13" ht="162">
+    <row r="11" spans="1:13" ht="40.5">
       <c r="A11" s="1">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>76</v>
-      </c>
       <c r="F11" s="6">
-        <v>42090</v>
+        <v>42094</v>
       </c>
       <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
+      <c r="H11" s="1" t="s">
+        <v>142</v>
+      </c>
       <c r="I11" s="5"/>
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
     </row>
-    <row r="12" spans="1:13" ht="94.5">
+    <row r="12" spans="1:13" ht="27">
       <c r="A12" s="1">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C12" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>80</v>
-      </c>
       <c r="E12" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F12" s="6">
         <v>42094</v>
       </c>
       <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
+      <c r="H12" s="1" t="s">
+        <v>142</v>
+      </c>
       <c r="I12" s="5"/>
       <c r="J12" s="5"/>
       <c r="K12" s="5"/>
       <c r="L12" s="5"/>
       <c r="M12" s="5"/>
     </row>
-    <row r="13" spans="1:13" ht="54">
+    <row r="13" spans="1:13" ht="27">
       <c r="A13" s="1">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>26</v>
+        <v>77</v>
       </c>
       <c r="F13" s="6">
         <v>42094</v>
       </c>
-      <c r="G13" s="1" t="s">
-        <v>23</v>
-      </c>
+      <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>12</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="I13" s="5"/>
       <c r="J13" s="5"/>
       <c r="K13" s="5"/>
       <c r="L13" s="5"/>
       <c r="M13" s="5"/>
     </row>
-    <row r="14" spans="1:13" ht="40.5">
+    <row r="14" spans="1:13" ht="67.5">
       <c r="A14" s="1">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C14" s="1"/>
+        <v>93</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>88</v>
+      </c>
       <c r="D14" s="1" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F14" s="6">
-        <v>42094</v>
+        <v>42102</v>
       </c>
       <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
+      <c r="H14" s="1" t="s">
+        <v>142</v>
+      </c>
       <c r="I14" s="5"/>
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
       <c r="M14" s="5"/>
     </row>
-    <row r="15" spans="1:13" ht="27">
+    <row r="15" spans="1:13" ht="81">
       <c r="A15" s="1">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C15" s="1"/>
+        <v>91</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>94</v>
+      </c>
       <c r="D15" s="1" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F15" s="6">
-        <v>42094</v>
+        <v>42102</v>
       </c>
       <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
+      <c r="H15" s="1" t="s">
+        <v>142</v>
+      </c>
       <c r="I15" s="5"/>
       <c r="J15" s="5"/>
       <c r="K15" s="5"/>
       <c r="L15" s="5"/>
       <c r="M15" s="5"/>
     </row>
-    <row r="16" spans="1:13" ht="27">
+    <row r="16" spans="1:13" ht="94.5">
       <c r="A16" s="1">
+        <v>27</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F16" s="6">
+        <v>42124</v>
+      </c>
+      <c r="G16" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F16" s="6">
-        <v>42094</v>
-      </c>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
+      <c r="H16" s="1" t="s">
+        <v>142</v>
+      </c>
       <c r="I16" s="5"/>
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
       <c r="L16" s="5"/>
       <c r="M16" s="5"/>
     </row>
-    <row r="17" spans="1:13" ht="67.5">
+    <row r="17" spans="1:13" ht="94.5">
       <c r="A17" s="1">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="F17" s="6">
-        <v>42102</v>
-      </c>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
+        <v>42124</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>142</v>
+      </c>
       <c r="I17" s="5"/>
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
     </row>
-    <row r="18" spans="1:13" ht="81">
+    <row r="18" spans="1:13" ht="54">
       <c r="A18" s="1">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="F18" s="6">
-        <v>42102</v>
-      </c>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
+        <v>42124</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>136</v>
+      </c>
       <c r="I18" s="5"/>
       <c r="J18" s="5"/>
       <c r="K18" s="5"/>
       <c r="L18" s="5"/>
       <c r="M18" s="5"/>
     </row>
-    <row r="19" spans="1:13" ht="81">
+    <row r="19" spans="1:13" ht="67.5">
       <c r="A19" s="1">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="E19" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="F19" s="6">
-        <v>42104</v>
-      </c>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
+        <v>42124</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>142</v>
+      </c>
       <c r="I19" s="5"/>
       <c r="J19" s="5"/>
       <c r="K19" s="5"/>
       <c r="L19" s="5"/>
       <c r="M19" s="5"/>
     </row>
-    <row r="20" spans="1:13" ht="94.5">
+    <row r="20" spans="1:13" ht="81">
       <c r="A20" s="1">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="F20" s="6">
         <v>42124</v>
       </c>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
+      <c r="G20" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>142</v>
+      </c>
       <c r="I20" s="5"/>
       <c r="J20" s="5"/>
       <c r="K20" s="5"/>
@@ -1673,133 +1774,163 @@
     </row>
     <row r="21" spans="1:13" ht="94.5">
       <c r="A21" s="1">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="F21" s="6">
         <v>42124</v>
       </c>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
+      <c r="G21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>137</v>
+      </c>
       <c r="I21" s="5"/>
       <c r="J21" s="5"/>
       <c r="K21" s="5"/>
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
     </row>
-    <row r="22" spans="1:13" ht="94.5">
+    <row r="22" spans="1:13" ht="81">
       <c r="A22" s="1">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="F22" s="6">
         <v>42124</v>
       </c>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
+      <c r="G22" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>138</v>
+      </c>
       <c r="I22" s="5"/>
       <c r="J22" s="5"/>
       <c r="K22" s="5"/>
       <c r="L22" s="5"/>
       <c r="M22" s="5"/>
     </row>
-    <row r="23" spans="1:13" ht="54">
+    <row r="23" spans="1:13" ht="121.5">
       <c r="A23" s="1">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="F23" s="6">
         <v>42124</v>
       </c>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="5"/>
-      <c r="K23" s="5"/>
-      <c r="L23" s="5"/>
-      <c r="M23" s="5"/>
-    </row>
-    <row r="24" spans="1:13" ht="54">
+      <c r="G23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J23" s="5">
+        <v>8</v>
+      </c>
+      <c r="K23" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="L23" s="5">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="M23" s="13">
+        <v>42210</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="108">
       <c r="A24" s="1">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="F24" s="6">
         <v>42124</v>
       </c>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
+      <c r="G24" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>142</v>
+      </c>
       <c r="I24" s="5"/>
       <c r="J24" s="5"/>
-      <c r="K24" s="5"/>
+      <c r="K24" s="14"/>
       <c r="L24" s="5"/>
-      <c r="M24" s="5"/>
-    </row>
-    <row r="25" spans="1:13" ht="67.5">
+      <c r="M24" s="13"/>
+    </row>
+    <row r="25" spans="1:13" ht="202.5">
       <c r="A25" s="1">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="F25" s="6">
-        <v>42124</v>
-      </c>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
+        <v>42143</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>142</v>
+      </c>
       <c r="I25" s="5"/>
       <c r="J25" s="5"/>
       <c r="K25" s="5"/>
@@ -1808,50 +1939,42 @@
     </row>
     <row r="26" spans="1:13" ht="81">
       <c r="A26" s="1">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>107</v>
+        <v>58</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="F26" s="6">
-        <v>42124</v>
-      </c>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
+        <v>42149</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>141</v>
+      </c>
       <c r="I26" s="5"/>
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
       <c r="L26" s="5"/>
       <c r="M26" s="5"/>
     </row>
-    <row r="27" spans="1:13" ht="94.5">
-      <c r="A27" s="1">
-        <v>34</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="F27" s="6">
-        <v>42124</v>
-      </c>
+    <row r="27" spans="1:13">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="5"/>
@@ -1860,25 +1983,13 @@
       <c r="L27" s="5"/>
       <c r="M27" s="5"/>
     </row>
-    <row r="28" spans="1:13" ht="81">
-      <c r="A28" s="1">
-        <v>35</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="F28" s="6">
-        <v>42124</v>
-      </c>
+    <row r="28" spans="1:13">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="5"/>
@@ -1887,25 +1998,13 @@
       <c r="L28" s="5"/>
       <c r="M28" s="5"/>
     </row>
-    <row r="29" spans="1:13" ht="121.5">
-      <c r="A29" s="1">
-        <v>36</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="F29" s="6">
-        <v>42124</v>
-      </c>
+    <row r="29" spans="1:13">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="5"/>
@@ -1914,25 +2013,13 @@
       <c r="L29" s="5"/>
       <c r="M29" s="5"/>
     </row>
-    <row r="30" spans="1:13" ht="108">
-      <c r="A30" s="1">
-        <v>37</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F30" s="6">
-        <v>42124</v>
-      </c>
+    <row r="30" spans="1:13">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="5"/>
@@ -1941,25 +2028,13 @@
       <c r="L30" s="5"/>
       <c r="M30" s="5"/>
     </row>
-    <row r="31" spans="1:13" ht="202.5">
-      <c r="A31" s="1">
-        <v>38</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="F31" s="6">
-        <v>42143</v>
-      </c>
+    <row r="31" spans="1:13">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="5"/>
@@ -1968,25 +2043,13 @@
       <c r="L31" s="5"/>
       <c r="M31" s="5"/>
     </row>
-    <row r="32" spans="1:13" ht="81">
-      <c r="A32" s="1">
-        <v>39</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F32" s="6">
-        <v>42149</v>
-      </c>
+    <row r="32" spans="1:13">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="5"/>
@@ -16245,108 +16308,22 @@
       <c r="L982" s="5"/>
       <c r="M982" s="5"/>
     </row>
-    <row r="983" spans="1:13">
-      <c r="A983" s="1"/>
-      <c r="B983" s="1"/>
-      <c r="C983" s="1"/>
-      <c r="D983" s="1"/>
-      <c r="E983" s="1"/>
-      <c r="F983" s="1"/>
-      <c r="G983" s="1"/>
-      <c r="H983" s="1"/>
-      <c r="I983" s="5"/>
-      <c r="J983" s="5"/>
-      <c r="K983" s="5"/>
-      <c r="L983" s="5"/>
-      <c r="M983" s="5"/>
-    </row>
-    <row r="984" spans="1:13">
-      <c r="A984" s="1"/>
-      <c r="B984" s="1"/>
-      <c r="C984" s="1"/>
-      <c r="D984" s="1"/>
-      <c r="E984" s="1"/>
-      <c r="F984" s="1"/>
-      <c r="G984" s="1"/>
-      <c r="H984" s="1"/>
-      <c r="I984" s="5"/>
-      <c r="J984" s="5"/>
-      <c r="K984" s="5"/>
-      <c r="L984" s="5"/>
-      <c r="M984" s="5"/>
-    </row>
-    <row r="985" spans="1:13">
-      <c r="A985" s="1"/>
-      <c r="B985" s="1"/>
-      <c r="C985" s="1"/>
-      <c r="D985" s="1"/>
-      <c r="E985" s="1"/>
-      <c r="F985" s="1"/>
-      <c r="G985" s="1"/>
-      <c r="H985" s="1"/>
-      <c r="I985" s="5"/>
-      <c r="J985" s="5"/>
-      <c r="K985" s="5"/>
-      <c r="L985" s="5"/>
-      <c r="M985" s="5"/>
-    </row>
-    <row r="986" spans="1:13">
-      <c r="A986" s="1"/>
-      <c r="B986" s="1"/>
-      <c r="C986" s="1"/>
-      <c r="D986" s="1"/>
-      <c r="E986" s="1"/>
-      <c r="F986" s="1"/>
-      <c r="G986" s="1"/>
-      <c r="H986" s="1"/>
-      <c r="I986" s="5"/>
-      <c r="J986" s="5"/>
-      <c r="K986" s="5"/>
-      <c r="L986" s="5"/>
-      <c r="M986" s="5"/>
-    </row>
-    <row r="987" spans="1:13">
-      <c r="A987" s="1"/>
-      <c r="B987" s="1"/>
-      <c r="C987" s="1"/>
-      <c r="D987" s="1"/>
-      <c r="E987" s="1"/>
-      <c r="F987" s="1"/>
-      <c r="G987" s="1"/>
-      <c r="H987" s="1"/>
-      <c r="I987" s="5"/>
-      <c r="J987" s="5"/>
-      <c r="K987" s="5"/>
-      <c r="L987" s="5"/>
-      <c r="M987" s="5"/>
-    </row>
-    <row r="988" spans="1:13">
-      <c r="A988" s="1"/>
-      <c r="B988" s="1"/>
-      <c r="C988" s="1"/>
-      <c r="D988" s="1"/>
-      <c r="E988" s="1"/>
-      <c r="F988" s="1"/>
-      <c r="G988" s="1"/>
-      <c r="H988" s="1"/>
-      <c r="I988" s="5"/>
-      <c r="J988" s="5"/>
-      <c r="K988" s="5"/>
-      <c r="L988" s="5"/>
-      <c r="M988" s="5"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I988">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I982">
       <formula1>"接纳,拒绝,重复,已实现"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G988">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G982">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="K2" r:id="rId1"/>
+    <hyperlink ref="K23" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -16471,10 +16448,10 @@
         <v>23</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J3" s="10" t="s">
         <v>34</v>
@@ -16494,7 +16471,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C4" s="10"/>
       <c r="D4" s="10" t="s">
@@ -16510,7 +16487,7 @@
         <v>23</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="I4" s="10" t="s">
         <v>12</v>
@@ -16519,7 +16496,7 @@
         <v>34</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L4" s="10">
         <v>1.1200000000000001</v>
@@ -16533,7 +16510,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C5" s="10"/>
       <c r="D5" s="10" t="s">
@@ -16549,16 +16526,16 @@
         <v>23</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="I5" s="10" t="s">
         <v>12</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L5" s="10">
         <v>1.1200000000000001</v>
@@ -16590,16 +16567,16 @@
         <v>23</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="I6" s="10" t="s">
         <v>12</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K6" s="12" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L6" s="10">
         <v>1.1200000000000001</v>
@@ -16613,34 +16590,34 @@
         <v>9</v>
       </c>
       <c r="B7" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" s="10" t="s">
         <v>47</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>49</v>
       </c>
       <c r="F7" s="11">
         <v>42072</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="L7" s="10">
         <v>1.1399999999999999</v>
@@ -16670,13 +16647,13 @@
         <v>23</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>12</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="K8" s="5"/>
       <c r="L8" s="5">
@@ -16689,16 +16666,16 @@
         <v>20</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="F9" s="11">
         <v>42094</v>
@@ -16707,7 +16684,7 @@
         <v>16</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="I9" s="10" t="s">
         <v>12</v>
@@ -16716,44 +16693,94 @@
         <v>3</v>
       </c>
       <c r="K9" s="12" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="M9" s="11">
         <v>42097</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
+    <row r="10" spans="1:13" ht="81">
+      <c r="A10" s="10">
+        <v>26</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="F10" s="11">
+        <v>42104</v>
+      </c>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="J10" s="10">
+        <v>9</v>
+      </c>
+      <c r="K10" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="L10" s="10">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="M10" s="15">
+        <v>42200</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="108">
+      <c r="A11" s="10">
+        <v>28</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="F11" s="11">
+        <v>42124</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="J11" s="10">
+        <v>4</v>
+      </c>
+      <c r="K11" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="L11" s="10">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="M11" s="15">
+        <v>42210</v>
+      </c>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="1"/>
@@ -31413,8 +31440,10 @@
     <hyperlink ref="K6" r:id="rId5"/>
     <hyperlink ref="K7" r:id="rId6"/>
     <hyperlink ref="K9" r:id="rId7"/>
+    <hyperlink ref="K10" r:id="rId8"/>
+    <hyperlink ref="K11" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId8"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId10"/>
 </worksheet>
 </file>
--- a/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
+++ b/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="148">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -647,6 +647,23 @@
     <t>和节点监控统一规则</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t xml:space="preserve">增加DECIMAL数据类型
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用于存储关系型DECIMAL数据类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>民生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>张云WEI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1968,14 +1985,28 @@
       <c r="L26" s="5"/>
       <c r="M26" s="5"/>
     </row>
-    <row r="27" spans="1:13">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
+    <row r="27" spans="1:13" ht="27">
+      <c r="A27" s="1">
+        <v>40</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F27" s="6">
+        <v>42214</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="H27" s="1"/>
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>

--- a/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
+++ b/internal_doc/12.需求跟踪/SequoiaDB外部需求跟踪表.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="150">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -664,6 +664,14 @@
     <t>张云WEI</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>SEQUOIADBMAINSTREAM-1610</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已完成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1153,7 +1161,7 @@
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="A1:M982"/>
+  <dimension ref="A1:M981"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.25" customWidth="1"/>
@@ -1985,28 +1993,14 @@
       <c r="L26" s="5"/>
       <c r="M26" s="5"/>
     </row>
-    <row r="27" spans="1:13" ht="27">
-      <c r="A27" s="1">
-        <v>40</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="F27" s="6">
-        <v>42214</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>16</v>
-      </c>
+    <row r="27" spans="1:13">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>
@@ -16324,28 +16318,13 @@
       <c r="L981" s="5"/>
       <c r="M981" s="5"/>
     </row>
-    <row r="982" spans="1:13">
-      <c r="A982" s="1"/>
-      <c r="B982" s="1"/>
-      <c r="C982" s="1"/>
-      <c r="D982" s="1"/>
-      <c r="E982" s="1"/>
-      <c r="F982" s="1"/>
-      <c r="G982" s="1"/>
-      <c r="H982" s="1"/>
-      <c r="I982" s="5"/>
-      <c r="J982" s="5"/>
-      <c r="K982" s="5"/>
-      <c r="L982" s="5"/>
-      <c r="M982" s="5"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I982">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I981">
       <formula1>"接纳,拒绝,重复,已实现"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G982">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G981">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
   </dataValidations>
@@ -16813,20 +16792,44 @@
         <v>42210</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
+    <row r="12" spans="1:13" ht="27">
+      <c r="A12" s="10">
+        <v>40</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="F12" s="10">
+        <v>42214</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="J12" s="10">
+        <v>60</v>
+      </c>
+      <c r="K12" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="L12" s="10">
+        <v>2.6</v>
+      </c>
+      <c r="M12" s="10"/>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="1"/>
@@ -31473,8 +31476,9 @@
     <hyperlink ref="K9" r:id="rId7"/>
     <hyperlink ref="K10" r:id="rId8"/>
     <hyperlink ref="K11" r:id="rId9"/>
+    <hyperlink ref="K12" r:id="rId10" display="http://jira:8080/browse/SEQUOIADBMAINSTREAM-1610"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId10"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId11"/>
 </worksheet>
 </file>